--- a/spotlight/Вебинары_опись.xlsx
+++ b/spotlight/Вебинары_опись.xlsx
@@ -3678,12 +3678,16 @@
           <t>Adjective order + appearance</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Adjectives+Appearance</t>
+        </is>
+      </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -3728,12 +3732,17 @@
           <t>Alternative questions + introducing yourself</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Alternative questions + introducing yourself
+Alternative questions+Introducing yourself</t>
+        </is>
+      </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -3757,7 +3766,12 @@
 самостоятельная (pptx): WOW_Speak_Or_Questions_10-12_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>к папке два видео — проверить, не дубль ли
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -3778,12 +3792,16 @@
           <t>Articles review + travel and holidays</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Articles review + travel and holidays</t>
+        </is>
+      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -3828,9 +3846,9 @@
           <t>Be going to предсказания с очевидным основанием</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -3878,12 +3896,16 @@
           <t>Comparisons extended  + famous people</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Comparison extended+famous people</t>
+        </is>
+      </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -3928,12 +3950,16 @@
           <t>Conditionals type 0 and type 1</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Conditionals type 0and type 1</t>
+        </is>
+      </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -3957,7 +3983,11 @@
 самостоятельная (pptx): WOW_Speak_Conditionals_0_1_Habits_10-12_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>есть ещё папка «Sport + Conditionals 0-1» — к ней видео нет</t>
+        </is>
+      </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -3978,12 +4008,16 @@
           <t>Daily activities Adverbs of frequency in Pr Simple</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Daily Activities. Adverbs of Frequency in Pr.S.</t>
+        </is>
+      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4028,9 +4062,9 @@
           <t>Exclamations what how + festivals</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -4078,12 +4112,16 @@
           <t>Experiences Gerunds and infinitives</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Gerunds and infinitives, experiences</t>
+        </is>
+      </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4127,12 +4165,16 @@
           <t>Food Quantifiers, countables-uncountalbes</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Food Quantifiers, countables-uncountables</t>
+        </is>
+      </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4177,12 +4219,17 @@
           <t>Future tenses + school and jobs</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Future tenses + school and jobs
+Future tenses + school and jobs</t>
+        </is>
+      </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4206,7 +4253,11 @@
 самостоятельная (pptx): WOW_Speak_Future_Tenses_Review_13-14_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>второе видео с тем же названием — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -4227,12 +4278,16 @@
           <t>Global issues + used to-get used to</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Get be used to + Global issues</t>
+        </is>
+      </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4255,7 +4310,11 @@
 презентация урока (pptx): WOW_Speak_UsedTo_GlobalIssues_Presentation.pptx</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>в материалах папки только used to; be/get used to в них нет</t>
+        </is>
+      </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -4276,9 +4335,9 @@
           <t>Gradable non-gradable adjectives + art and music</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -4327,9 +4386,9 @@
           <t>Health + Conditionals 2-3</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -4377,9 +4436,9 @@
           <t>History + narrative tenses</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -4427,9 +4486,9 @@
           <t>Holidays Have you ever</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -4478,9 +4537,9 @@
           <t>Holidays Have you ever/10-12 Have you ever travelling</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -4526,12 +4585,16 @@
           <t>Holidays Word formation</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Holidays + Word formation</t>
+        </is>
+      </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
           <t>лексика</t>
@@ -4576,9 +4639,9 @@
           <t>Indirect questions + neighbours</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -4626,12 +4689,16 @@
           <t>Inventions + Past Perfect-Past Perfect Cont</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Inventions + Past PerfectPast Perfect Cont</t>
+        </is>
+      </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4674,12 +4741,16 @@
           <t>It-sentences + seasons, months, weather</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>It sentences+seasons, months, weather</t>
+        </is>
+      </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4724,12 +4795,16 @@
           <t>Linkers time and sequence +your typical day</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Linkers— time and seq...nce + your typical day</t>
+        </is>
+      </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4753,7 +4828,11 @@
 самостоятельная (pptx): WOW_Speak_Linkers_Time_Sequence_DailyRoutine_10-12_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>есть ещё похожая папка «Time and sequence + your typical day» — к ней видео нет</t>
+        </is>
+      </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -4774,9 +4853,9 @@
           <t>May + robots</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -4824,12 +4903,16 @@
           <t>Movies Irregular verbs</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Movies+Irregular verbs</t>
+        </is>
+      </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4874,12 +4957,16 @@
           <t>Past tenses (review) + travel and holidays</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Past Tenses Review + travel and holidays</t>
+        </is>
+      </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4924,12 +5011,17 @@
           <t>Plans for summer + Going to</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Plans for summer + Going to
+Plans for summer+to be going to</t>
+        </is>
+      </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4953,7 +5045,12 @@
 презентация урока (pptx): student_presentation_going_to.pptx</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>к папке два видео — проверить, не дубль ли
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -4974,9 +5071,9 @@
           <t>Possessive case and pronouns + describing collections and personal belongings</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -5024,9 +5121,9 @@
           <t>Possessive of vs _s</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -5074,12 +5171,16 @@
           <t>Possessive pronouns + forms of identification</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Possesive pronounce+f...tification_09.06.2026</t>
+        </is>
+      </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5124,12 +5225,16 @@
           <t>Present Perfect already yet just + summer camps</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Pr.Perfect already+just+yet+summer camp</t>
+        </is>
+      </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5174,12 +5279,16 @@
           <t>Present Perfect Continuous eco-helping activities</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Present Perfect Contin... eco-helping activities</t>
+        </is>
+      </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5224,12 +5333,16 @@
           <t>Present Perfect for since + experiences</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Present Perfect for since + experiences</t>
+        </is>
+      </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5274,12 +5387,16 @@
           <t>Present Perfect vs Past Simple+ films</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Present PerfectvsPast Simple+films</t>
+        </is>
+      </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5324,12 +5441,16 @@
           <t>Present Simple for schedules and timetables</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Present Simple for shedules and timetables</t>
+        </is>
+      </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5374,12 +5495,16 @@
           <t>Present tenses (review) + character and relationships</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Present tenses (review...cter and relationships</t>
+        </is>
+      </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5424,12 +5549,16 @@
           <t>Quantifiers extended + food and drinks  shopping</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Quantifiers extended ...d and drinks shopping</t>
+        </is>
+      </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5474,12 +5603,16 @@
           <t>Quantifiers extended + travel</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Quantifiers extended + travel</t>
+        </is>
+      </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5524,12 +5657,16 @@
           <t>Reflexive pronouns</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Reflexive pronouns</t>
+        </is>
+      </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5574,9 +5711,9 @@
           <t>Relative pronouns and adverbs</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -5624,12 +5761,16 @@
           <t>Road safety Imperatives</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Road safety + imperatives</t>
+        </is>
+      </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5673,12 +5814,16 @@
           <t>Rules Must-mustn_t</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Rules must-mustnt</t>
+        </is>
+      </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5723,12 +5868,16 @@
           <t>Shopping + Articles</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Shopping. Articles.</t>
+        </is>
+      </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5752,7 +5901,11 @@
 презентация урока (pptx): WOW_Speak_Articles_Shopping_10-12_LESSON.pptx</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>отнесено по порядку, проверить</t>
+        </is>
+      </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -5773,12 +5926,16 @@
           <t>Shopping Articles</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr"/>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Shopping .Articles.</t>
+        </is>
+      </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5802,7 +5959,11 @@
 план урока (docx): WOW_Speak_Articles_Shopping_v2.docx</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>двух видео «Shopping Articles» и двух папок не различить по названию — отнесено по порядку, проверить</t>
+        </is>
+      </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -5823,12 +5984,16 @@
           <t>Shopping+Present Perfect-Present Perfect Continuous</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Shopping+Present Per...nt Perfect Continuous</t>
+        </is>
+      </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5873,12 +6038,16 @@
           <t>Should(n_t) + safety and crime prevention</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Shouldn't + safety and crime prevention</t>
+        </is>
+      </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5923,12 +6092,16 @@
           <t>Singular vs plural nouns_ countable  uncountable_ collective_ plural-only nouns + food and quantities</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Singular vs plural no... countable uncountable</t>
+        </is>
+      </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -5973,12 +6146,16 @@
           <t>Sport + Conditionals 0-1</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Sport + Conditionals 0-1</t>
+        </is>
+      </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -6023,12 +6200,16 @@
           <t>Sports + Compound adjectives</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr"/>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Sport+Compound adjectives.</t>
+        </is>
+      </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -6073,12 +6254,17 @@
           <t>Stative verbs + perception and feelings</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Stative verbs + perception and feelings
+Stative verbs.Preceive+feelings.</t>
+        </is>
+      </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -6102,7 +6288,12 @@
 самостоятельная (pptx): WOW_Speak_StativeVerbs_Self-study_10-12.pptx</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>к папке два видео — проверить, не дубль ли
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -6123,12 +6314,17 @@
           <t>Tenses overview 1</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Tense overview (Prese...mple, Present Perfect)
+Tenses overview 1</t>
+        </is>
+      </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -6152,7 +6348,12 @@
 самостоятельная (pptx): WOW_Speak_Tenses_Overview_Families_13-14_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>в папке как раз Present Simple vs Past Simple vs Present Perfect; к папке два видео — проверить
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -6173,9 +6374,9 @@
           <t>Tenses overview 2</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -6223,9 +6424,9 @@
           <t>Time and sequence + your typical day</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -6273,9 +6474,9 @@
           <t>Time clauses + technology</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -6323,9 +6524,9 @@
           <t>Time clauses about future</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -6373,12 +6574,16 @@
           <t>Too + Enough + clothes</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Too + Enough + clothes</t>
+        </is>
+      </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -6423,12 +6628,17 @@
           <t>Transport Phrasal verbs</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Phrasal Verbs Movement and Travel
+Travelling Phrasal Verbs</t>
+        </is>
+      </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
           <t>лексика</t>
@@ -6451,7 +6661,12 @@
 самостоятельная (pptx): WOW_Speak_PhrasalVerbs_Travel_Selfstudy.pptx</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>название другое; в папке как раз фразовые глаголы движения и путешествий
+к папке два видео («Phrasal Verbs Movement and Travel» и это) — проверить, разные ли уроки</t>
+        </is>
+      </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -6472,12 +6687,16 @@
           <t>Used to + infinitive + vanished things</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Used to + infinitive + vanished things</t>
+        </is>
+      </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -6522,12 +6741,16 @@
           <t>Your schedule + Present Continuous for future meaning</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr"/>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Your schedule + Prese...ous for future meaning</t>
+        </is>
+      </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -6572,9 +6795,9 @@
           <t>Zero article vs the</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -9644,12 +9867,16 @@
           <t>Adjective order + appearance</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Adjectives+Appearance</t>
+        </is>
+      </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -9694,12 +9921,17 @@
           <t>Alternative questions + introducing yourself</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Alternative questions + introducing yourself
+Alternative questions+Introducing yourself</t>
+        </is>
+      </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -9723,7 +9955,12 @@
 самостоятельная (pptx): WOW_Speak_Or_Questions_10-12_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>к папке два видео — проверить, не дубль ли
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -9744,12 +9981,16 @@
           <t>Articles review + travel and holidays</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr"/>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Articles review + travel and holidays</t>
+        </is>
+      </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -9794,9 +10035,9 @@
           <t>Be going to предсказания с очевидным основанием</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -9844,12 +10085,16 @@
           <t>Comparisons extended  + famous people</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Comparison extended+famous people</t>
+        </is>
+      </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -9894,12 +10139,16 @@
           <t>Conditionals type 0 and type 1</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Conditionals type 0and type 1</t>
+        </is>
+      </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -9923,7 +10172,11 @@
 самостоятельная (pptx): WOW_Speak_Conditionals_0_1_Habits_10-12_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>есть ещё папка «Sport + Conditionals 0-1» — к ней видео нет</t>
+        </is>
+      </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -9944,12 +10197,16 @@
           <t>Daily activities Adverbs of frequency in Pr Simple</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr"/>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Daily Activities. Adverbs of Frequency in Pr.S.</t>
+        </is>
+      </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -9994,9 +10251,9 @@
           <t>Exclamations what how + festivals</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -10044,12 +10301,16 @@
           <t>Experiences Gerunds and infinitives</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Gerunds and infinitives, experiences</t>
+        </is>
+      </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10093,12 +10354,16 @@
           <t>Food Quantifiers, countables-uncountalbes</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Food Quantifiers, countables-uncountables</t>
+        </is>
+      </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10143,12 +10408,17 @@
           <t>Future tenses + school and jobs</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Future tenses + school and jobs
+Future tenses + school and jobs</t>
+        </is>
+      </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10172,7 +10442,11 @@
 самостоятельная (pptx): WOW_Speak_Future_Tenses_Review_13-14_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>второе видео с тем же названием — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -10193,12 +10467,16 @@
           <t>Global issues + used to-get used to</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Get be used to + Global issues</t>
+        </is>
+      </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10221,7 +10499,11 @@
 презентация урока (pptx): WOW_Speak_UsedTo_GlobalIssues_Presentation.pptx</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>в материалах папки только used to; be/get used to в них нет</t>
+        </is>
+      </c>
       <c r="K67" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -10242,9 +10524,9 @@
           <t>Gradable non-gradable adjectives + art and music</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -10293,9 +10575,9 @@
           <t>Health + Conditionals 2-3</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -10343,9 +10625,9 @@
           <t>History + narrative tenses</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -10393,9 +10675,9 @@
           <t>Holidays Have you ever</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -10444,9 +10726,9 @@
           <t>Holidays Have you ever/10-12 Have you ever travelling</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -10492,12 +10774,16 @@
           <t>Holidays Word formation</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Holidays + Word formation</t>
+        </is>
+      </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
           <t>лексика</t>
@@ -10542,9 +10828,9 @@
           <t>Indirect questions + neighbours</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -10592,12 +10878,16 @@
           <t>Inventions + Past Perfect-Past Perfect Cont</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Inventions + Past PerfectPast Perfect Cont</t>
+        </is>
+      </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10640,12 +10930,16 @@
           <t>It-sentences + seasons, months, weather</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>It sentences+seasons, months, weather</t>
+        </is>
+      </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10690,12 +10984,16 @@
           <t>Linkers time and sequence +your typical day</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Linkers— time and seq...nce + your typical day</t>
+        </is>
+      </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10719,7 +11017,11 @@
 самостоятельная (pptx): WOW_Speak_Linkers_Time_Sequence_DailyRoutine_10-12_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>есть ещё похожая папка «Time and sequence + your typical day» — к ней видео нет</t>
+        </is>
+      </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -10740,9 +11042,9 @@
           <t>May + robots</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -10790,12 +11092,16 @@
           <t>Movies Irregular verbs</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Movies+Irregular verbs</t>
+        </is>
+      </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10840,12 +11146,16 @@
           <t>Past tenses (review) + travel and holidays</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Past Tenses Review + travel and holidays</t>
+        </is>
+      </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10890,12 +11200,17 @@
           <t>Plans for summer + Going to</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Plans for summer + Going to
+Plans for summer+to be going to</t>
+        </is>
+      </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10919,7 +11234,12 @@
 презентация урока (pptx): student_presentation_going_to.pptx</t>
         </is>
       </c>
-      <c r="J81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>к папке два видео — проверить, не дубль ли
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K81" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -10940,9 +11260,9 @@
           <t>Possessive case and pronouns + describing collections and personal belongings</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -10990,9 +11310,9 @@
           <t>Possessive of vs _s</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
@@ -11040,12 +11360,16 @@
           <t>Possessive pronouns + forms of identification</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Possesive pronounce+f...tification_09.06.2026</t>
+        </is>
+      </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11090,12 +11414,16 @@
           <t>Present Perfect already yet just + summer camps</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr"/>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Pr.Perfect already+just+yet+summer camp</t>
+        </is>
+      </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11140,12 +11468,16 @@
           <t>Present Perfect Continuous eco-helping activities</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Present Perfect Contin... eco-helping activities</t>
+        </is>
+      </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11190,12 +11522,16 @@
           <t>Present Perfect for since + experiences</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Present Perfect for since + experiences</t>
+        </is>
+      </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11240,12 +11576,16 @@
           <t>Present Perfect vs Past Simple+ films</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Present PerfectvsPast Simple+films</t>
+        </is>
+      </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11290,12 +11630,16 @@
           <t>Present Simple for schedules and timetables</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Present Simple for shedules and timetables</t>
+        </is>
+      </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11340,12 +11684,16 @@
           <t>Present tenses (review) + character and relationships</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Present tenses (review...cter and relationships</t>
+        </is>
+      </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11390,12 +11738,16 @@
           <t>Quantifiers extended + food and drinks  shopping</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Quantifiers extended ...d and drinks shopping</t>
+        </is>
+      </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11440,12 +11792,16 @@
           <t>Quantifiers extended + travel</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Quantifiers extended + travel</t>
+        </is>
+      </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11490,12 +11846,16 @@
           <t>Reflexive pronouns</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Reflexive pronouns</t>
+        </is>
+      </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11540,9 +11900,9 @@
           <t>Relative pronouns and adverbs</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
@@ -11590,12 +11950,16 @@
           <t>Road safety Imperatives</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Road safety + imperatives</t>
+        </is>
+      </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11639,12 +12003,16 @@
           <t>Rules Must-mustn_t</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Rules must-mustnt</t>
+        </is>
+      </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11689,12 +12057,16 @@
           <t>Shopping + Articles</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Shopping. Articles.</t>
+        </is>
+      </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11718,7 +12090,11 @@
 презентация урока (pptx): WOW_Speak_Articles_Shopping_10-12_LESSON.pptx</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr"/>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>отнесено по порядку, проверить</t>
+        </is>
+      </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -11739,12 +12115,16 @@
           <t>Shopping Articles</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Shopping .Articles.</t>
+        </is>
+      </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11768,7 +12148,11 @@
 план урока (docx): WOW_Speak_Articles_Shopping_v2.docx</t>
         </is>
       </c>
-      <c r="J98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>двух видео «Shopping Articles» и двух папок не различить по названию — отнесено по порядку, проверить</t>
+        </is>
+      </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -11789,12 +12173,16 @@
           <t>Shopping+Present Perfect-Present Perfect Continuous</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Shopping+Present Per...nt Perfect Continuous</t>
+        </is>
+      </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11839,12 +12227,16 @@
           <t>Should(n_t) + safety and crime prevention</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Shouldn't + safety and crime prevention</t>
+        </is>
+      </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11889,12 +12281,16 @@
           <t>Singular vs plural nouns_ countable  uncountable_ collective_ plural-only nouns + food and quantities</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Singular vs plural no... countable uncountable</t>
+        </is>
+      </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11939,12 +12335,16 @@
           <t>Sport + Conditionals 0-1</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr"/>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Sport + Conditionals 0-1</t>
+        </is>
+      </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -11989,12 +12389,16 @@
           <t>Sports + Compound adjectives</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr"/>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Sport+Compound adjectives.</t>
+        </is>
+      </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -12039,12 +12443,17 @@
           <t>Stative verbs + perception and feelings</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Stative verbs + perception and feelings
+Stative verbs.Preceive+feelings.</t>
+        </is>
+      </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -12068,7 +12477,12 @@
 самостоятельная (pptx): WOW_Speak_StativeVerbs_Self-study_10-12.pptx</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>к папке два видео — проверить, не дубль ли
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -12089,12 +12503,17 @@
           <t>Tenses overview 1</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Tense overview (Prese...mple, Present Perfect)
+Tenses overview 1</t>
+        </is>
+      </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -12118,7 +12537,12 @@
 самостоятельная (pptx): WOW_Speak_Tenses_Overview_Families_13-14_SELFSTUDY.pptx</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>в папке как раз Present Simple vs Past Simple vs Present Perfect; к папке два видео — проверить
+второе видео к той же папке — проверить, не дубль ли</t>
+        </is>
+      </c>
       <c r="K105" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -12139,9 +12563,9 @@
           <t>Tenses overview 2</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
@@ -12189,9 +12613,9 @@
           <t>Time and sequence + your typical day</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
@@ -12239,9 +12663,9 @@
           <t>Time clauses + technology</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
@@ -12289,9 +12713,9 @@
           <t>Time clauses about future</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr"/>
@@ -12339,12 +12763,16 @@
           <t>Too + Enough + clothes</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr"/>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Too + Enough + clothes</t>
+        </is>
+      </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -12389,12 +12817,17 @@
           <t>Transport Phrasal verbs</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr"/>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Phrasal Verbs Movement and Travel
+Travelling Phrasal Verbs</t>
+        </is>
+      </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
           <t>лексика</t>
@@ -12417,7 +12850,12 @@
 самостоятельная (pptx): WOW_Speak_PhrasalVerbs_Travel_Selfstudy.pptx</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>название другое; в папке как раз фразовые глаголы движения и путешествий
+к папке два видео («Phrasal Verbs Movement and Travel» и это) — проверить, разные ли уроки</t>
+        </is>
+      </c>
       <c r="K111" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -12438,12 +12876,16 @@
           <t>Used to + infinitive + vanished things</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr"/>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Used to + infinitive + vanished things</t>
+        </is>
+      </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -12488,12 +12930,16 @@
           <t>Your schedule + Present Continuous for future meaning</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr"/>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Your schedule + Prese...ous for future meaning</t>
+        </is>
+      </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -12538,9 +12984,9 @@
           <t>Zero article vs the</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr"/>
@@ -12701,11 +13147,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12719,6 +13166,402 @@
           <t>Название видео</t>
         </is>
       </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Замечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Adjectives -ing -ed + ...ons and characteristics</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет (в 10+ нет урока на -ed/-ing прилагательные)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Adverb comparatives + landmarks</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Animals body parts. Tag questions.</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Can can't — permission...f holiday travel rules</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет (есть «May + robots» — это may, не can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Comparatives superlatives Places in town</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет (есть только «Comparisons extended»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Compound Nouns + free time</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет (есть «Sports + Compound adjectives» — это прилагательные)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Extreme sports have to and don't have to</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами в 10+ нет (в 7-9 есть «Have to don't have to + chores»); два видео — проверить, не дубль ли</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Extreme sports have to don't have to</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>второе видео той же темы; папки с материалами в 10+ нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Hobbies. free time, idioms about free time</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>папка с материалами есть только в 7-9: «Hobbies, free time, idioms about free time»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Mustn't have to do+rules about animals</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет (есть «Rules Must-mustn_t» — другой урок)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Object Pronounce+describing relashiionship</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Past Continuous + news stories</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Places to go.Past Simple regular verbs.</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Present Simple+Present Con-s+Clothes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами в 10+ нет (в 7-9 есть «Present Simple vs Present Continuous»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Weekend fun + linkers</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Adverbs of degree + p...ance and relationships</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Educaiton + mixed conditionals</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Farm animals+irregular plurals</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>папка с материалами есть только в 7-9: «Farm animals+irregular plurals»</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Fashion trends+Causative have</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Media Modals of advice</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Present Simple Present Continuous + Clothes</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами в 10+ нет; похоже на видео «Present Simple+Present Con-s+Clothes» — проверить, не дубль ли</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Science, word formation (adjectives)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет (в «Holidays Word formation» — только -ful/-able)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Socializing+forming nouns from verbs</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/spotlight/Вебинары_опись.xlsx
+++ b/spotlight/Вебинары_опись.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Видео без папки" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'7-9'!$A$1:$K$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10+'!$A$1:$K$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Все'!$A$1:$K$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'7-9'!$A$1:$L$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'10+'!$A$1:$L$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Все'!$A$1:$L$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -587,7 +587,8 @@
     <col width="90" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,6 +644,11 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>В расписании</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>Ссылка на папку</t>
         </is>
       </c>
@@ -695,7 +701,8 @@
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -749,7 +756,8 @@
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -803,7 +811,8 @@
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -852,7 +861,8 @@
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -902,7 +912,8 @@
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -956,7 +967,8 @@
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1010,7 +1022,8 @@
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1060,7 +1073,12 @@
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>29.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1110,7 +1128,8 @@
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1164,7 +1183,8 @@
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1218,7 +1238,8 @@
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1272,7 +1293,8 @@
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1326,7 +1348,8 @@
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1376,7 +1399,8 @@
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1426,7 +1450,8 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1484,7 +1509,8 @@
           <t>название другое, тема та же — there is / there are</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1536,7 +1562,8 @@
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1590,7 +1617,8 @@
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1644,7 +1672,8 @@
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1698,7 +1727,12 @@
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>19.10 · запланирован · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1744,7 +1778,8 @@
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1798,7 +1833,8 @@
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1852,7 +1888,8 @@
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1902,7 +1939,8 @@
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -1956,7 +1994,8 @@
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2010,7 +2049,8 @@
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2068,7 +2108,8 @@
           <t>есть ещё папка «May I + dinner table situations» — к ней видео нет</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2118,7 +2159,12 @@
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>15.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2176,7 +2222,8 @@
           <t>проверить: название другое (Food / Meals), тема та же — much/many/a lot of</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2226,7 +2273,8 @@
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2279,7 +2327,8 @@
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2333,7 +2382,8 @@
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2387,7 +2437,8 @@
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2441,7 +2492,8 @@
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2501,7 +2553,12 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>05.10 · проведён · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2555,7 +2612,8 @@
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2615,7 +2673,12 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>08.10 · проведён · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2673,7 +2736,12 @@
           <t>папок две почти одинаковых (с «(_s)» и «s»), видео одно — отнесено к первой</t>
         </is>
       </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>12.10 · запланирован · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2723,7 +2791,8 @@
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr"/>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2777,7 +2846,8 @@
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr"/>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2827,7 +2897,8 @@
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2881,7 +2952,8 @@
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2935,7 +3007,8 @@
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -2985,7 +3058,12 @@
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr"/>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>22.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3035,7 +3113,12 @@
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>26.10 · запланирован · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3089,7 +3172,8 @@
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3139,7 +3223,8 @@
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3193,7 +3278,8 @@
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr"/>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3247,7 +3333,8 @@
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3301,7 +3388,8 @@
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3355,7 +3443,8 @@
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr"/>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3409,7 +3498,8 @@
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr"/>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3463,7 +3553,8 @@
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3517,69 +3608,74 @@
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>01.10 · проведён · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K55"/>
+  <autoFilter ref="A1:L55"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3591,7 +3687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3604,7 +3700,8 @@
     <col width="90" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3660,6 +3757,11 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>В расписании</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>Ссылка на папку</t>
         </is>
       </c>
@@ -3712,7 +3814,8 @@
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3772,7 +3875,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3826,7 +3930,8 @@
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3876,7 +3981,8 @@
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3930,7 +4036,8 @@
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -3988,7 +4095,8 @@
           <t>есть ещё папка «Sport + Conditionals 0-1» — к ней видео нет</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4042,7 +4150,8 @@
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4092,7 +4201,12 @@
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>06.10 · проведён · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4145,7 +4259,8 @@
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4199,7 +4314,8 @@
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4258,7 +4374,8 @@
           <t>второе видео с тем же названием — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4315,7 +4432,8 @@
           <t>в материалах папки только used to; be/get used to в них нет</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4366,7 +4484,8 @@
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4416,7 +4535,8 @@
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4466,7 +4586,8 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4517,7 +4638,8 @@
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4565,7 +4687,8 @@
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4619,7 +4742,8 @@
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4669,7 +4793,12 @@
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>09.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4721,7 +4850,8 @@
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4775,7 +4905,8 @@
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4833,7 +4964,8 @@
           <t>есть ещё похожая папка «Time and sequence + your typical day» — к ней видео нет</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4883,7 +5015,8 @@
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4937,7 +5070,8 @@
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -4991,7 +5125,8 @@
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5051,7 +5186,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5101,7 +5237,8 @@
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr"/>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5151,7 +5288,12 @@
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>23.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5205,7 +5347,8 @@
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5259,7 +5402,8 @@
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5313,7 +5457,12 @@
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>02.10 · проведён · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5367,7 +5516,8 @@
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5421,7 +5571,8 @@
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5475,7 +5626,8 @@
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5529,7 +5681,8 @@
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr"/>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5583,7 +5736,8 @@
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5637,7 +5791,8 @@
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr"/>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5691,7 +5846,8 @@
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5741,7 +5897,12 @@
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr"/>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>16.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5794,7 +5955,8 @@
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr"/>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5848,7 +6010,8 @@
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5906,7 +6069,8 @@
           <t>отнесено по порядку, проверить</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -5964,7 +6128,8 @@
           <t>двух видео «Shopping Articles» и двух папок не различить по названию — отнесено по порядку, проверить</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6018,7 +6183,12 @@
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr"/>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>30.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6072,7 +6242,8 @@
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6126,7 +6297,8 @@
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6180,7 +6352,8 @@
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6234,7 +6407,8 @@
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr"/>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6294,7 +6468,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6354,7 +6529,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6404,7 +6580,12 @@
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr"/>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>27.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6454,7 +6635,8 @@
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr"/>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6504,7 +6686,8 @@
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6554,7 +6737,12 @@
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>13.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6608,7 +6796,8 @@
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr"/>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6667,7 +6856,8 @@
 к папке два видео («Phrasal Verbs Movement and Travel» и это) — проверить, разные ли уроки</t>
         </is>
       </c>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6721,7 +6911,8 @@
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6775,7 +6966,8 @@
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -6825,74 +7017,79 @@
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr"/>
-      <c r="K60" s="9" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>20.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K60"/>
+  <autoFilter ref="A1:L60"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6904,7 +7101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6917,7 +7114,8 @@
     <col width="90" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6973,6 +7171,11 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>В расписании</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>Ссылка на папку</t>
         </is>
       </c>
@@ -7025,7 +7228,8 @@
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7079,7 +7283,8 @@
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7133,7 +7338,8 @@
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7182,7 +7388,8 @@
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7232,7 +7439,8 @@
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7286,7 +7494,8 @@
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7340,7 +7549,8 @@
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7390,7 +7600,12 @@
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>29.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7440,7 +7655,8 @@
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7494,7 +7710,8 @@
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7548,7 +7765,8 @@
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7602,7 +7820,8 @@
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7656,7 +7875,8 @@
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7706,7 +7926,8 @@
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7756,7 +7977,8 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7814,7 +8036,8 @@
           <t>название другое, тема та же — there is / there are</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7866,7 +8089,8 @@
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7920,7 +8144,8 @@
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -7974,7 +8199,8 @@
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8028,7 +8254,12 @@
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>19.10 · запланирован · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8074,7 +8305,8 @@
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8128,7 +8360,8 @@
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8182,7 +8415,8 @@
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8232,7 +8466,8 @@
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8286,7 +8521,8 @@
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8340,7 +8576,8 @@
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8398,7 +8635,8 @@
           <t>есть ещё папка «May I + dinner table situations» — к ней видео нет</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8448,7 +8686,12 @@
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>15.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8506,7 +8749,8 @@
           <t>проверить: название другое (Food / Meals), тема та же — much/many/a lot of</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8556,7 +8800,8 @@
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8609,7 +8854,8 @@
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8663,7 +8909,8 @@
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8717,7 +8964,8 @@
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8771,7 +9019,8 @@
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8831,7 +9080,12 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>05.10 · проведён · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8885,7 +9139,8 @@
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -8945,7 +9200,12 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>08.10 · проведён · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9003,7 +9263,12 @@
           <t>папок две почти одинаковых (с «(_s)» и «s»), видео одно — отнесено к первой</t>
         </is>
       </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>12.10 · запланирован · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9053,7 +9318,8 @@
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr"/>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9107,7 +9373,8 @@
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr"/>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9157,7 +9424,8 @@
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9211,7 +9479,8 @@
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9265,7 +9534,8 @@
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9315,7 +9585,12 @@
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr"/>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>22.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9365,7 +9640,12 @@
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>26.10 · запланирован · Губенко Алёна</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9419,7 +9699,8 @@
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9469,7 +9750,8 @@
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9523,7 +9805,8 @@
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr"/>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9577,7 +9860,8 @@
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9631,7 +9915,8 @@
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9685,7 +9970,8 @@
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr"/>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9739,7 +10025,8 @@
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr"/>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9793,7 +10080,8 @@
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9847,7 +10135,12 @@
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>01.10 · проведён · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9901,7 +10194,8 @@
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr"/>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -9961,7 +10255,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10015,7 +10310,8 @@
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10065,7 +10361,8 @@
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10119,7 +10416,8 @@
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr"/>
-      <c r="K60" s="9" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10177,7 +10475,8 @@
           <t>есть ещё папка «Sport + Conditionals 0-1» — к ней видео нет</t>
         </is>
       </c>
-      <c r="K61" s="9" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10231,7 +10530,8 @@
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="9" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10281,7 +10581,12 @@
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="9" t="inlineStr">
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>06.10 · проведён · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10334,7 +10639,8 @@
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr"/>
-      <c r="K64" s="9" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr"/>
+      <c r="L64" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10388,7 +10694,8 @@
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr"/>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10447,7 +10754,8 @@
           <t>второе видео с тем же названием — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K66" s="9" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10504,7 +10812,8 @@
           <t>в материалах папки только used to; be/get used to в них нет</t>
         </is>
       </c>
-      <c r="K67" s="9" t="inlineStr">
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10555,7 +10864,8 @@
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10605,7 +10915,8 @@
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr"/>
-      <c r="K69" s="9" t="inlineStr">
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10655,7 +10966,8 @@
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr"/>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10706,7 +11018,8 @@
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr"/>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10754,7 +11067,8 @@
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr"/>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10808,7 +11122,8 @@
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr"/>
-      <c r="K73" s="9" t="inlineStr">
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10858,7 +11173,12 @@
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr"/>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>09.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10910,7 +11230,8 @@
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr"/>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -10964,7 +11285,8 @@
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr"/>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr"/>
+      <c r="L76" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11022,7 +11344,8 @@
           <t>есть ещё похожая папка «Time and sequence + your typical day» — к ней видео нет</t>
         </is>
       </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K77" s="4" t="inlineStr"/>
+      <c r="L77" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11072,7 +11395,8 @@
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr"/>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr"/>
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11126,7 +11450,8 @@
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr"/>
-      <c r="K79" s="9" t="inlineStr">
+      <c r="K79" s="4" t="inlineStr"/>
+      <c r="L79" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11180,7 +11505,8 @@
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr"/>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11240,7 +11566,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K81" s="4" t="inlineStr"/>
+      <c r="L81" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11290,7 +11617,8 @@
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11340,7 +11668,12 @@
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="9" t="inlineStr">
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>23.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11394,7 +11727,8 @@
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11448,7 +11782,8 @@
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr"/>
-      <c r="K85" s="9" t="inlineStr">
+      <c r="K85" s="4" t="inlineStr"/>
+      <c r="L85" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11502,7 +11837,12 @@
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="9" t="inlineStr">
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>02.10 · проведён · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11556,7 +11896,8 @@
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr"/>
-      <c r="K87" s="9" t="inlineStr">
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11610,7 +11951,8 @@
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr"/>
-      <c r="K88" s="9" t="inlineStr">
+      <c r="K88" s="4" t="inlineStr"/>
+      <c r="L88" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11664,7 +12006,8 @@
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr"/>
-      <c r="K89" s="9" t="inlineStr">
+      <c r="K89" s="4" t="inlineStr"/>
+      <c r="L89" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11718,7 +12061,8 @@
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr">
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11772,7 +12116,8 @@
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr"/>
-      <c r="K91" s="9" t="inlineStr">
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11826,7 +12171,8 @@
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="9" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11880,7 +12226,8 @@
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr"/>
-      <c r="K93" s="9" t="inlineStr">
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11930,7 +12277,12 @@
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr"/>
-      <c r="K94" s="9" t="inlineStr">
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>16.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L94" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -11983,7 +12335,8 @@
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr"/>
-      <c r="K95" s="9" t="inlineStr">
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12037,7 +12390,8 @@
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr"/>
-      <c r="K96" s="9" t="inlineStr">
+      <c r="K96" s="4" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12095,7 +12449,8 @@
           <t>отнесено по порядку, проверить</t>
         </is>
       </c>
-      <c r="K97" s="9" t="inlineStr">
+      <c r="K97" s="4" t="inlineStr"/>
+      <c r="L97" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12153,7 +12508,8 @@
           <t>двух видео «Shopping Articles» и двух папок не различить по названию — отнесено по порядку, проверить</t>
         </is>
       </c>
-      <c r="K98" s="9" t="inlineStr">
+      <c r="K98" s="4" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12207,7 +12563,12 @@
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr"/>
-      <c r="K99" s="9" t="inlineStr">
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>30.10 · запланирован · Сирацкая Евгения</t>
+        </is>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12261,7 +12622,8 @@
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="9" t="inlineStr">
+      <c r="K100" s="4" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12315,7 +12677,8 @@
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr"/>
-      <c r="K101" s="9" t="inlineStr">
+      <c r="K101" s="4" t="inlineStr"/>
+      <c r="L101" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12369,7 +12732,8 @@
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr"/>
-      <c r="K102" s="9" t="inlineStr">
+      <c r="K102" s="4" t="inlineStr"/>
+      <c r="L102" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12423,7 +12787,8 @@
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr"/>
-      <c r="K103" s="9" t="inlineStr">
+      <c r="K103" s="4" t="inlineStr"/>
+      <c r="L103" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12483,7 +12848,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K104" s="9" t="inlineStr">
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12543,7 +12909,8 @@
 второе видео к той же папке — проверить, не дубль ли</t>
         </is>
       </c>
-      <c r="K105" s="9" t="inlineStr">
+      <c r="K105" s="4" t="inlineStr"/>
+      <c r="L105" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12593,7 +12960,12 @@
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr"/>
-      <c r="K106" s="9" t="inlineStr">
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>27.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L106" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12643,7 +13015,8 @@
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr"/>
-      <c r="K107" s="9" t="inlineStr">
+      <c r="K107" s="4" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12693,7 +13066,8 @@
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr"/>
-      <c r="K108" s="9" t="inlineStr">
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12743,7 +13117,12 @@
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr"/>
-      <c r="K109" s="9" t="inlineStr">
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>13.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L109" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12797,7 +13176,8 @@
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr"/>
-      <c r="K110" s="9" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12856,7 +13236,8 @@
 к папке два видео («Phrasal Verbs Movement and Travel» и это) — проверить, разные ли уроки</t>
         </is>
       </c>
-      <c r="K111" s="9" t="inlineStr">
+      <c r="K111" s="4" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12910,7 +13291,8 @@
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr"/>
-      <c r="K112" s="9" t="inlineStr">
+      <c r="K112" s="4" t="inlineStr"/>
+      <c r="L112" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -12964,7 +13346,8 @@
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr"/>
-      <c r="K113" s="9" t="inlineStr">
+      <c r="K113" s="4" t="inlineStr"/>
+      <c r="L113" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
@@ -13014,128 +13397,133 @@
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr"/>
-      <c r="K114" s="9" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>20.10 · запланирован · Лепкова Инна</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K114"/>
+  <autoFilter ref="A1:L114"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/spotlight/Вебинары_опись.xlsx
+++ b/spotlight/Вебинары_опись.xlsx
@@ -4429,7 +4429,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>в материалах папки только used to; be/get used to в них нет</t>
+          <t>засчитано только за used to: be/get used to в нём нет (подтвердила методист)</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>в материалах папки только used to; be/get used to в них нет</t>
+          <t>засчитано только за used to: be/get used to в нём нет (подтвердила методист)</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr"/>

--- a/spotlight/Вебинары_опись.xlsx
+++ b/spotlight/Вебинары_опись.xlsx
@@ -4395,16 +4395,12 @@
           <t>Global issues + used to-get used to</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>есть</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Get be used to + Global issues</t>
-        </is>
-      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -4427,11 +4423,7 @@
 презентация урока (pptx): WOW_Speak_UsedTo_GlobalIssues_Presentation.pptx</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>засчитано только за used to: be/get used to в нём нет (подтвердила методист)</t>
-        </is>
-      </c>
+      <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="9" t="inlineStr">
         <is>
@@ -10775,16 +10767,12 @@
           <t>Global issues + used to-get used to</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>есть</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Get be used to + Global issues</t>
-        </is>
-      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
           <t>грамматика</t>
@@ -10807,11 +10795,7 @@
 презентация урока (pptx): WOW_Speak_UsedTo_GlobalIssues_Presentation.pptx</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>засчитано только за used to: be/get used to в нём нет (подтвердила методист)</t>
-        </is>
-      </c>
+      <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr"/>
       <c r="L67" s="9" t="inlineStr">
         <is>
@@ -13535,7 +13519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13891,12 +13875,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Media Modals of advice</t>
+          <t>Get be used to + Global issues</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>папки с материалами нет</t>
+          <t>не подходит к теме: в материалах только used to, be/get used to нет — не засчитываем</t>
         </is>
       </c>
     </row>
@@ -13908,12 +13892,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Present Simple Present Continuous + Clothes</t>
+          <t>Media Modals of advice</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>папки с материалами в 10+ нет; похоже на видео «Present Simple+Present Con-s+Clothes» — проверить, не дубль ли</t>
+          <t>папки с материалами нет</t>
         </is>
       </c>
     </row>
@@ -13925,12 +13909,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Science, word formation (adjectives)</t>
+          <t>Present Simple Present Continuous + Clothes</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>папки с материалами нет (в «Holidays Word formation» — только -ful/-able)</t>
+          <t>папки с материалами в 10+ нет; похоже на видео «Present Simple+Present Con-s+Clothes» — проверить, не дубль ли</t>
         </is>
       </c>
     </row>
@@ -13942,10 +13926,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t>Science, word formation (adjectives)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>папки с материалами нет (в «Holidays Word formation» — только -ful/-able)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>Socializing+forming nouns from verbs</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>папки с материалами нет</t>
         </is>

--- a/spotlight/Вебинары_опись.xlsx
+++ b/spotlight/Вебинары_опись.xlsx
@@ -1075,7 +1075,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>29.10 · запланирован · Лепкова Инна</t>
+          <t>29.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -1729,7 +1729,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>19.10 · запланирован · Губенко Алёна</t>
+          <t>19.10 · по расписанию · Губенко Алёна</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -2161,7 +2161,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>15.10 · запланирован · Лепкова Инна</t>
+          <t>15.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>12.10 · запланирован · Губенко Алёна</t>
+          <t>12.10 · по расписанию · Губенко Алёна</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -3060,7 +3060,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>22.10 · запланирован · Лепкова Инна</t>
+          <t>22.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -3115,7 +3115,7 @@
       <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>26.10 · запланирован · Губенко Алёна</t>
+          <t>26.10 · по расписанию · Губенко Алёна</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -4787,7 +4787,7 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>09.10 · запланирован · Сирацкая Евгения</t>
+          <t>09.10 · проведён · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -5282,7 +5282,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>23.10 · запланирован · Сирацкая Евгения</t>
+          <t>23.10 · по расписанию · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -5891,7 +5891,7 @@
       <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>16.10 · запланирован · Сирацкая Евгения</t>
+          <t>16.10 · по расписанию · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -6177,7 +6177,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>30.10 · запланирован · Сирацкая Евгения</t>
+          <t>30.10 · по расписанию · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -6574,7 +6574,7 @@
       <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>27.10 · запланирован · Лепкова Инна</t>
+          <t>27.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
@@ -6731,7 +6731,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>13.10 · запланирован · Лепкова Инна</t>
+          <t>13.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>20.10 · запланирован · Лепкова Инна</t>
+          <t>20.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr">
@@ -7594,7 +7594,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>29.10 · запланирован · Лепкова Инна</t>
+          <t>29.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -8248,7 +8248,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>19.10 · запланирован · Губенко Алёна</t>
+          <t>19.10 · по расписанию · Губенко Алёна</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>15.10 · запланирован · Лепкова Инна</t>
+          <t>15.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>12.10 · запланирован · Губенко Алёна</t>
+          <t>12.10 · по расписанию · Губенко Алёна</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -9579,7 +9579,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>22.10 · запланирован · Лепкова Инна</t>
+          <t>22.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -9634,7 +9634,7 @@
       <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>26.10 · запланирован · Губенко Алёна</t>
+          <t>26.10 · по расписанию · Губенко Алёна</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -11159,7 +11159,7 @@
       <c r="J74" s="4" t="inlineStr"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>09.10 · запланирован · Сирацкая Евгения</t>
+          <t>09.10 · проведён · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
@@ -11654,7 +11654,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>23.10 · запланирован · Сирацкая Евгения</t>
+          <t>23.10 · по расписанию · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr">
@@ -12263,7 +12263,7 @@
       <c r="J94" s="4" t="inlineStr"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>16.10 · запланирован · Сирацкая Евгения</t>
+          <t>16.10 · по расписанию · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L94" s="9" t="inlineStr">
@@ -12549,7 +12549,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>30.10 · запланирован · Сирацкая Евгения</t>
+          <t>30.10 · по расписанию · Сирацкая Евгения</t>
         </is>
       </c>
       <c r="L99" s="9" t="inlineStr">
@@ -12946,7 +12946,7 @@
       <c r="J106" s="4" t="inlineStr"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>27.10 · запланирован · Лепкова Инна</t>
+          <t>27.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L106" s="9" t="inlineStr">
@@ -13103,7 +13103,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>13.10 · запланирован · Лепкова Инна</t>
+          <t>13.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L109" s="9" t="inlineStr">
@@ -13383,7 +13383,7 @@
       <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>20.10 · запланирован · Лепкова Инна</t>
+          <t>20.10 · по расписанию · Лепкова Инна</t>
         </is>
       </c>
       <c r="L114" s="9" t="inlineStr">

--- a/spotlight/Вебинары_опись.xlsx
+++ b/spotlight/Вебинары_опись.xlsx
@@ -861,7 +861,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -1450,7 +1454,11 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -2897,7 +2905,11 @@
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -3981,7 +3993,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -4527,7 +4543,11 @@
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -4578,7 +4598,11 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -4630,7 +4654,11 @@
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -5229,7 +5257,11 @@
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -7380,7 +7412,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -7969,7 +8005,11 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -9416,7 +9456,11 @@
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -10353,7 +10397,11 @@
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -10899,7 +10947,11 @@
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr"/>
-      <c r="K69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L69" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -10950,7 +11002,11 @@
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -11002,7 +11058,11 @@
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L71" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
@@ -11601,7 +11661,11 @@
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03.11 · по расписанию · </t>
+        </is>
+      </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
           <t>открыть</t>
